--- a/Design/Excel/ET/Datas/Product/GridAutoRecipeConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/GridAutoRecipeConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1188,6 +1188,21 @@
           <t>ServingContainerDefinitionId</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>StationCapability</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>LockContainer</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1235,6 +1250,21 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1282,6 +1312,21 @@
           <t>ServingContainerDefinitionId</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>StationCapability</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>LockContainer</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1327,6 +1372,83 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Product/GridAutoRecipeConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/GridAutoRecipeConfig.xlsx
@@ -963,475 +963,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <x:col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <x:col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <x:col min="11" max="16384" width="9" style="2" customWidth="0"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ContainerDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InputDefinitionIds</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InputCounts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RequiredTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OutputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OutputPortions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ServingContainerDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StationCapability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LockContainer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MenuVariant</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(list#sep=,),int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(list#sep=,),int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bool</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ContainerDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InputDefinitionIds</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InputCounts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RequiredTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OutputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OutputPortions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ServingContainerDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StationCapability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LockContainer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MenuVariant</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2,4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1,1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">120</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">17</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">16</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">120</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">18</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">19</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1024</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">true</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str"/>
-      <x:c r="B6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>43,3,44</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>1,1,1</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G6" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J6" t="n">
-        <x:v>8192</x:v>
-      </x:c>
-      <x:c r="K6" s="6" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L6" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str"/>
-      <x:c r="B7" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G7" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H7" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I7" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J7" t="n">
-        <x:v>32768</x:v>
-      </x:c>
-      <x:c r="K7" s="6" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L7" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str"/>
-      <x:c r="B8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F8" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G8" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I8" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J8" t="n">
-        <x:v>65536</x:v>
-      </x:c>
-      <x:c r="K8" s="6" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L8" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str"/>
-      <x:c r="B9" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G9" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I9" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J9" t="n">
-        <x:v>131072</x:v>
-      </x:c>
-      <x:c r="K9" s="6" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L9" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ContainerDefinitionId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InputDefinitionIds</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InputCounts</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RequiredTicks</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OutputDefinitionId</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OutputPortions</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ServingContainerDefinitionId</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StationCapability</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LockContainer</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MenuVariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>GridStationCapability</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bool</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ProductMenuVariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ContainerDefinitionId</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InputDefinitionIds</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InputCounts</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RequiredTicks</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OutputDefinitionId</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OutputPortions</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ServingContainerDefinitionId</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StationCapability</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LockContainer</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MenuVariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,4</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Juice</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str"/>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D6" t="str">
+        <v>43,3,44</v>
+      </c>
+      <c r="E6" t="str">
+        <v>1,1,1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>80</v>
+      </c>
+      <c r="G6" t="n">
+        <v>46</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>47</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Mixing</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str"/>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>54</v>
+      </c>
+      <c r="D7" t="str">
+        <v>53</v>
+      </c>
+      <c r="E7" t="str">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" t="n">
+        <v>56</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>59</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Extract</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str"/>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D8" t="str">
+        <v>44</v>
+      </c>
+      <c r="E8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" t="n">
+        <v>57</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>59</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>HeatMilk</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str"/>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>55</v>
+      </c>
+      <c r="D9" t="str">
+        <v>44</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" t="n">
+        <v>58</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>59</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FoamMilk</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>